--- a/xls/square_16_quad4_18.xlsx
+++ b/xls/square_16_quad4_18.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>361</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>289</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>768</v>
+      </c>
+      <c r="I16">
+        <v>1.2135152942520375</v>
+      </c>
+      <c r="J16">
+        <v>-0.5970321351883865</v>
+      </c>
+      <c r="K16">
+        <v>0.20044183066158466</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>361</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>289</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>867</v>
+      </c>
+      <c r="I17">
+        <v>-0.31462967047998425</v>
+      </c>
+      <c r="J17">
+        <v>-1.2439077374969378</v>
+      </c>
+      <c r="K17">
+        <v>1.445256858870271</v>
+      </c>
+    </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>1.3798429958845588</v>
+        <v>0.3420845460674094</v>
       </c>
       <c r="J18">
-        <v>-1.6578016141711214</v>
+        <v>-1.5607447635043459</v>
       </c>
       <c r="K18">
-        <v>2.233987794673716</v>
+        <v>1.6755291800773704</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -517,13 +587,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.8908933392286889</v>
+        <v>-1.465049216935511</v>
       </c>
       <c r="J19">
-        <v>-1.8828052148573442</v>
+        <v>-1.552882498635323</v>
       </c>
       <c r="K19">
-        <v>0.8483243674678635</v>
+        <v>1.1741195835382328</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-1.8804972649143712</v>
+        <v>-1.4378442344781837</v>
       </c>
       <c r="J20">
-        <v>-1.8734607128175693</v>
+        <v>-1.5327318751983456</v>
       </c>
       <c r="K20">
-        <v>1.1606008106087478</v>
+        <v>3.02123770697196</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-1.825671474548386</v>
+        <v>-1.5603418858442766</v>
       </c>
       <c r="J21">
-        <v>-1.784278286101029</v>
+        <v>-1.539881953125465</v>
       </c>
       <c r="K21">
-        <v>1.7641331992957912</v>
+        <v>3.895384396043677</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-1.5747033337348264</v>
+        <v>-1.3988150575659097</v>
       </c>
       <c r="J22">
-        <v>-1.495926019719585</v>
+        <v>-1.0600741770192263</v>
       </c>
       <c r="K22">
-        <v>2.4999763311122796</v>
+        <v>4.629884034220711</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-1.2336022062228724</v>
+        <v>-0.29677919289893995</v>
       </c>
       <c r="J23">
-        <v>-1.1582239172517221</v>
+        <v>-0.27854793605323397</v>
       </c>
       <c r="K23">
-        <v>3.156687762573511</v>
+        <v>4.904849508709615</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.48940838469525416</v>
+        <v>-0.015330016294830601</v>
       </c>
       <c r="J24">
-        <v>-0.43129216797323955</v>
+        <v>-0.014070524589384677</v>
       </c>
       <c r="K24">
-        <v>3.916381459616641</v>
+        <v>4.468264483221026</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.08686508588969652</v>
+        <v>-0.0003056447681645151</v>
       </c>
       <c r="J25">
-        <v>-0.07260547196630183</v>
+        <v>-0.0002464792464220034</v>
       </c>
       <c r="K25">
-        <v>3.633431077360009</v>
+        <v>3.574768232036589</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -762,13 +832,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.012452481178562761</v>
+        <v>-4.761345482211221e-5</v>
       </c>
       <c r="J26">
-        <v>-0.01165662424346545</v>
+        <v>-4.455646725748225e-5</v>
       </c>
       <c r="K26">
-        <v>3.464542439611508</v>
+        <v>3.2271598264545194</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -797,13 +867,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.001620544557813209</v>
+        <v>-2.1728369634640187e-5</v>
       </c>
       <c r="J27">
-        <v>-0.0015308513415367025</v>
+        <v>-2.0033988499070747e-5</v>
       </c>
       <c r="K27">
-        <v>3.0469573671899903</v>
+        <v>3.0833082595142174</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -832,13 +902,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.0011073459973767528</v>
+        <v>-1.6332246593073993e-5</v>
       </c>
       <c r="J28">
-        <v>-0.0010867904373876628</v>
+        <v>-1.5913430331530245e-5</v>
       </c>
       <c r="K28">
-        <v>2.9794129374413143</v>
+        <v>3.0463570798565947</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -867,13 +937,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.00046618868542761357</v>
+        <v>-5.108287713104968e-6</v>
       </c>
       <c r="J29">
-        <v>-0.00047277349646432306</v>
+        <v>-5.168618232693648e-6</v>
       </c>
       <c r="K29">
-        <v>2.807141474369123</v>
+        <v>2.794919419889077</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -902,13 +972,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.000369328718782498</v>
+        <v>-3.417748823195009e-6</v>
       </c>
       <c r="J30">
-        <v>-0.00037557855504927786</v>
+        <v>-3.4366000272905836e-6</v>
       </c>
       <c r="K30">
-        <v>2.7549671903105883</v>
+        <v>2.6972547153913022</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.0004493332370801398</v>
+        <v>-3.8739568036481824e-6</v>
       </c>
       <c r="J31">
-        <v>-0.00044952990031465383</v>
+        <v>-3.850335860718791e-6</v>
       </c>
       <c r="K31">
-        <v>2.7914783363047797</v>
+        <v>2.721199000439344</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.000278790957244315</v>
+        <v>-2.6384372325334647e-6</v>
       </c>
       <c r="J32">
-        <v>-0.0002791730284633622</v>
+        <v>-2.6176195462470906e-6</v>
       </c>
       <c r="K32">
-        <v>2.686645530264162</v>
+        <v>2.6343301349686388</v>
       </c>
     </row>
   </sheetData>
